--- a/data/base/Backlog_11.xlsx
+++ b/data/base/Backlog_11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6ACD767-D6E8-4547-B9FC-5F4C37D0A071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05870E62-FF69-41AE-8831-55DE59DB6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
+    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{F94ADF0D-E689-408D-A963-E639FABAA829}"/>
   </bookViews>
   <sheets>
     <sheet name="SPN" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="33">
   <si>
     <t>Status</t>
   </si>
@@ -137,6 +137,9 @@
   </si>
   <si>
     <t>Arthur Hassuma</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -242,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -280,6 +283,20 @@
     <xf numFmtId="17" fontId="5" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,7 +707,7 @@
         <v>46104</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>17</v>
@@ -760,7 +777,7 @@
         <v>46104</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>17</v>
@@ -795,7 +812,7 @@
         <v>46104</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>17</v>
@@ -830,7 +847,7 @@
         <v>46104</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>17</v>
@@ -865,7 +882,7 @@
         <v>46104</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>17</v>
@@ -935,7 +952,7 @@
         <v>46104</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>17</v>
@@ -970,7 +987,7 @@
         <v>46104</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>17</v>
@@ -1116,143 +1133,143 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+    <row r="15" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="1">
-        <v>11</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F15" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G15" s="6">
+      <c r="C15" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="17">
+        <v>11</v>
+      </c>
+      <c r="E15" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F15" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G15" s="18">
         <v>12179</v>
       </c>
-      <c r="H15" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I15" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J15" s="5" t="s">
+      <c r="H15" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I15" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="K15" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+    <row r="16" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D16" s="1">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F16" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="C16" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D16" s="17">
+        <v>11</v>
+      </c>
+      <c r="E16" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F16" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G16" s="18">
         <v>12775</v>
       </c>
-      <c r="H16" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I16" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="H16" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I16" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D17" s="17">
+        <v>11</v>
+      </c>
+      <c r="E17" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F17" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G17" s="18">
+        <v>13038</v>
+      </c>
+      <c r="H17" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I17" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J17" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="K17" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D17" s="1">
-        <v>11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F17" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G17" s="6">
-        <v>13038</v>
-      </c>
-      <c r="H17" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I17" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D18" s="1">
-        <v>11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F18" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="C18" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D18" s="17">
+        <v>11</v>
+      </c>
+      <c r="E18" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F18" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G18" s="18">
         <v>13203</v>
       </c>
-      <c r="H18" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I18" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="H18" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I18" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1291,213 +1308,213 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
+    <row r="20" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D20" s="1">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F20" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="C20" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D20" s="17">
+        <v>11</v>
+      </c>
+      <c r="E20" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F20" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G20" s="18">
         <v>12922</v>
       </c>
-      <c r="H20" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I20" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J20" s="5" t="s">
+      <c r="H20" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I20" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J20" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D21" s="17">
+        <v>11</v>
+      </c>
+      <c r="E21" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F21" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G21" s="18">
+        <v>13124</v>
+      </c>
+      <c r="H21" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I21" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J21" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D22" s="17">
+        <v>11</v>
+      </c>
+      <c r="E22" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F22" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G22" s="18">
+        <v>12638</v>
+      </c>
+      <c r="H22" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I22" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J22" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="K22" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+    <row r="23" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D21" s="1">
-        <v>11</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F21" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G21" s="6">
-        <v>13124</v>
-      </c>
-      <c r="H21" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I21" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J21" s="5" t="s">
+      <c r="B23" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D23" s="17">
+        <v>11</v>
+      </c>
+      <c r="E23" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F23" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G23" s="18">
+        <v>11713</v>
+      </c>
+      <c r="H23" s="20">
+        <v>46054</v>
+      </c>
+      <c r="I23" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J23" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="K23" s="17" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+    <row r="24" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D22" s="1">
-        <v>11</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F22" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G22" s="6">
-        <v>12638</v>
-      </c>
-      <c r="H22" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I22" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J22" s="5" t="s">
+      <c r="B24" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D24" s="17">
+        <v>11</v>
+      </c>
+      <c r="E24" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F24" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G24" s="18">
+        <v>12252</v>
+      </c>
+      <c r="H24" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I24" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" s="22" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25" s="18">
+        <v>2026</v>
+      </c>
+      <c r="D25" s="17">
+        <v>11</v>
+      </c>
+      <c r="E25" s="19">
+        <v>46104</v>
+      </c>
+      <c r="F25" s="19">
+        <v>46108</v>
+      </c>
+      <c r="G25" s="18">
+        <v>13177</v>
+      </c>
+      <c r="H25" s="20">
+        <v>46082</v>
+      </c>
+      <c r="I25" s="19">
+        <v>46104</v>
+      </c>
+      <c r="J25" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D23" s="1">
-        <v>11</v>
-      </c>
-      <c r="E23" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F23" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G23" s="6">
-        <v>11713</v>
-      </c>
-      <c r="H23" s="16">
-        <v>46054</v>
-      </c>
-      <c r="I23" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C24" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D24" s="1">
-        <v>11</v>
-      </c>
-      <c r="E24" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F24" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G24" s="6">
-        <v>12252</v>
-      </c>
-      <c r="H24" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I24" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="6">
-        <v>2026</v>
-      </c>
-      <c r="D25" s="1">
-        <v>11</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46104</v>
-      </c>
-      <c r="F25" s="7">
-        <v>46108</v>
-      </c>
-      <c r="G25" s="6">
-        <v>13177</v>
-      </c>
-      <c r="H25" s="16">
-        <v>46082</v>
-      </c>
-      <c r="I25" s="7">
-        <v>46104</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K25" s="1" t="s">
+      <c r="K25" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1594,7 +1611,7 @@
         <v>46104</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>2</v>
@@ -1629,7 +1646,7 @@
         <v>46104</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>2</v>
@@ -1699,7 +1716,7 @@
         <v>46104</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>2</v>
@@ -1769,7 +1786,7 @@
         <v>46104</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>2</v>
@@ -1804,7 +1821,7 @@
         <v>46104</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>2</v>
@@ -1909,7 +1926,7 @@
         <v>46104</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>2</v>
@@ -1979,7 +1996,7 @@
         <v>46104</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>2</v>
@@ -2014,7 +2031,7 @@
         <v>46104</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>2</v>
@@ -2049,7 +2066,7 @@
         <v>46104</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>2</v>
@@ -2084,7 +2101,7 @@
         <v>46104</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>2</v>
@@ -2119,7 +2136,7 @@
         <v>46104</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>2</v>
@@ -2154,7 +2171,7 @@
         <v>46104</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>2</v>
@@ -2189,7 +2206,7 @@
         <v>46104</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>2</v>
@@ -2259,7 +2276,7 @@
         <v>46104</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>2</v>
@@ -2294,7 +2311,7 @@
         <v>46104</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>2</v>
